--- a/Team-Data/2008-09/12-14-2008-09.xlsx
+++ b/Team-Data/2008-09/12-14-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,16 +806,16 @@
         <v>1.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF2" t="n">
         <v>8</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH2" t="n">
         <v>24</v>
@@ -757,10 +824,10 @@
         <v>28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL2" t="n">
         <v>3</v>
@@ -769,13 +836,13 @@
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO2" t="n">
         <v>22</v>
       </c>
       <c r="AP2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ2" t="n">
         <v>24</v>
@@ -808,10 +875,10 @@
         <v>7</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -843,85 +910,85 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.913</v>
+        <v>0.917</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J3" t="n">
         <v>76</v>
       </c>
       <c r="K3" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M3" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.366</v>
+        <v>0.36</v>
       </c>
       <c r="O3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="P3" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.765</v>
+        <v>0.758</v>
       </c>
       <c r="R3" t="n">
         <v>10.7</v>
       </c>
       <c r="S3" t="n">
-        <v>32.8</v>
+        <v>32.5</v>
       </c>
       <c r="T3" t="n">
-        <v>43.6</v>
+        <v>43.3</v>
       </c>
       <c r="U3" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="V3" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="W3" t="n">
         <v>8.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.3</v>
+        <v>100.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI3" t="n">
         <v>17</v>
@@ -945,7 +1012,7 @@
         <v>4</v>
       </c>
       <c r="AL3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM3" t="n">
         <v>21</v>
@@ -960,19 +1027,19 @@
         <v>3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AR3" t="n">
         <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV3" t="n">
         <v>25</v>
@@ -981,10 +1048,10 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
         <v>26</v>
@@ -993,10 +1060,10 @@
         <v>2</v>
       </c>
       <c r="BB3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-4.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1115,7 +1182,7 @@
         <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL4" t="n">
         <v>23</v>
@@ -1133,10 +1200,10 @@
         <v>25</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP4" t="n">
         <v>12</v>
@@ -1169,16 +1236,16 @@
         <v>30</v>
       </c>
       <c r="AZ4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -1207,61 +1274,61 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>0.455</v>
+        <v>0.478</v>
       </c>
       <c r="H5" t="n">
         <v>48.2</v>
       </c>
       <c r="I5" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J5" t="n">
-        <v>84.5</v>
+        <v>83.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.438</v>
+        <v>0.44</v>
       </c>
       <c r="L5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.369</v>
+        <v>0.37</v>
       </c>
       <c r="O5" t="n">
-        <v>19</v>
+        <v>19.7</v>
       </c>
       <c r="P5" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="R5" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S5" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="T5" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U5" t="n">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="V5" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W5" t="n">
         <v>8</v>
@@ -1270,46 +1337,46 @@
         <v>5.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>20</v>
+        <v>20.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.5</v>
+        <v>-1.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK5" t="n">
         <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM5" t="n">
         <v>22</v>
@@ -1318,31 +1385,31 @@
         <v>12</v>
       </c>
       <c r="AO5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AP5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
         <v>4</v>
       </c>
       <c r="AR5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV5" t="n">
         <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
@@ -1351,16 +1418,16 @@
         <v>24</v>
       </c>
       <c r="AZ5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -1389,130 +1456,130 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" t="n">
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.87</v>
+        <v>0.833</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>38.3</v>
+        <v>37.9</v>
       </c>
       <c r="J6" t="n">
-        <v>80.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.478</v>
+        <v>0.476</v>
       </c>
       <c r="L6" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="N6" t="n">
-        <v>0.341</v>
+        <v>0.337</v>
       </c>
       <c r="O6" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="P6" t="n">
-        <v>25.4</v>
+        <v>25.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.785</v>
+        <v>0.782</v>
       </c>
       <c r="R6" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S6" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T6" t="n">
         <v>42.5</v>
       </c>
       <c r="U6" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="V6" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="W6" t="n">
         <v>7.9</v>
       </c>
       <c r="X6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>103.5</v>
+        <v>102.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.5</v>
+        <v>12.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
         <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK6" t="n">
         <v>3</v>
       </c>
       <c r="AL6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AM6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO6" t="n">
         <v>8</v>
       </c>
-      <c r="AN6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO6" t="n">
+      <c r="AP6" t="n">
         <v>10</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>11</v>
       </c>
       <c r="AQ6" t="n">
         <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
         <v>11</v>
@@ -1521,7 +1588,7 @@
         <v>12</v>
       </c>
       <c r="AV6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW6" t="n">
         <v>9</v>
@@ -1536,7 +1603,7 @@
         <v>12</v>
       </c>
       <c r="BA6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB6" t="n">
         <v>5</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>2.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
         <v>12</v>
@@ -1667,7 +1734,7 @@
         <v>4</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK7" t="n">
         <v>14</v>
@@ -1685,13 +1752,13 @@
         <v>21</v>
       </c>
       <c r="AP7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ7" t="n">
         <v>7</v>
       </c>
       <c r="AR7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
         <v>1</v>
@@ -1700,7 +1767,7 @@
         <v>2</v>
       </c>
       <c r="AU7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV7" t="n">
         <v>8</v>
@@ -1718,10 +1785,10 @@
         <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC7" t="n">
         <v>11</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>5.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1846,7 +1913,7 @@
         <v>15</v>
       </c>
       <c r="AI8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ8" t="n">
         <v>19</v>
@@ -1882,7 +1949,7 @@
         <v>13</v>
       </c>
       <c r="AU8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV8" t="n">
         <v>22</v>
@@ -1894,7 +1961,7 @@
         <v>3</v>
       </c>
       <c r="AY8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ8" t="n">
         <v>22</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>12</v>
@@ -2028,37 +2095,37 @@
         <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ9" t="n">
         <v>21</v>
       </c>
       <c r="AK9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL9" t="n">
         <v>19</v>
       </c>
       <c r="AM9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN9" t="n">
         <v>7</v>
       </c>
       <c r="AO9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>16</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>18</v>
       </c>
       <c r="AR9" t="n">
         <v>23</v>
       </c>
       <c r="AS9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT9" t="n">
         <v>26</v>
@@ -2076,13 +2143,13 @@
         <v>13</v>
       </c>
       <c r="AY9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ9" t="n">
         <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB9" t="n">
         <v>24</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,7 +2274,7 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL10" t="n">
         <v>21</v>
@@ -2246,19 +2313,19 @@
         <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
         <v>2</v>
       </c>
       <c r="AY10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ10" t="n">
         <v>13</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>3.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>6</v>
@@ -2389,31 +2456,31 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
         <v>29</v>
       </c>
       <c r="AJ11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM11" t="n">
         <v>12</v>
       </c>
       <c r="AN11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO11" t="n">
         <v>6</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ11" t="n">
         <v>2</v>
@@ -2425,7 +2492,7 @@
         <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU11" t="n">
         <v>25</v>
@@ -2434,7 +2501,7 @@
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX11" t="n">
         <v>29</v>
@@ -2452,7 +2519,7 @@
         <v>23</v>
       </c>
       <c r="BC11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
         <v>23</v>
@@ -2571,7 +2638,7 @@
         <v>23</v>
       </c>
       <c r="AH12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI12" t="n">
         <v>7</v>
@@ -2580,16 +2647,16 @@
         <v>3</v>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="n">
         <v>8</v>
       </c>
       <c r="AM12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="n">
         <v>27</v>
@@ -2601,10 +2668,10 @@
         <v>6</v>
       </c>
       <c r="AR12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT12" t="n">
         <v>4</v>
@@ -2616,7 +2683,7 @@
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX12" t="n">
         <v>12</v>
@@ -2628,7 +2695,7 @@
         <v>27</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
         <v>11</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
         <v>26</v>
@@ -2753,13 +2820,13 @@
         <v>26</v>
       </c>
       <c r="AH13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
@@ -2768,13 +2835,13 @@
         <v>22</v>
       </c>
       <c r="AM13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP13" t="n">
         <v>29</v>
@@ -2795,7 +2862,7 @@
         <v>20</v>
       </c>
       <c r="AV13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW13" t="n">
         <v>14</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -2863,43 +2930,43 @@
         <v>40.1</v>
       </c>
       <c r="J14" t="n">
-        <v>84.8</v>
+        <v>84.5</v>
       </c>
       <c r="K14" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="L14" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.372</v>
+        <v>0.382</v>
       </c>
       <c r="O14" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="P14" t="n">
         <v>28.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.756</v>
+        <v>0.754</v>
       </c>
       <c r="R14" t="n">
         <v>13</v>
       </c>
       <c r="S14" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T14" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="U14" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="V14" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="W14" t="n">
         <v>9.6</v>
@@ -2908,22 +2975,22 @@
         <v>5.7</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z14" t="n">
         <v>20.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.6</v>
+        <v>108.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2932,7 +2999,7 @@
         <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="n">
         <v>24</v>
@@ -2941,19 +3008,19 @@
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK14" t="n">
         <v>5</v>
       </c>
       <c r="AL14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2962,7 +3029,7 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR14" t="n">
         <v>5</v>
@@ -2974,7 +3041,7 @@
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV14" t="n">
         <v>14</v>
@@ -2983,10 +3050,10 @@
         <v>1</v>
       </c>
       <c r="AX14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY14" t="n">
         <v>7</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>6</v>
       </c>
       <c r="AZ14" t="n">
         <v>9</v>
@@ -2998,7 +3065,7 @@
         <v>1</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
         <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>0.375</v>
+        <v>0.348</v>
       </c>
       <c r="H15" t="n">
         <v>48.2</v>
@@ -3045,88 +3112,88 @@
         <v>35.7</v>
       </c>
       <c r="J15" t="n">
-        <v>77.8</v>
+        <v>78</v>
       </c>
       <c r="K15" t="n">
         <v>0.458</v>
       </c>
       <c r="L15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="M15" t="n">
         <v>13.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.35</v>
+        <v>0.339</v>
       </c>
       <c r="O15" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="P15" t="n">
-        <v>25.2</v>
+        <v>24.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.76</v>
+        <v>0.756</v>
       </c>
       <c r="R15" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S15" t="n">
         <v>28.8</v>
       </c>
       <c r="T15" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="U15" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="V15" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="W15" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y15" t="n">
         <v>4.3</v>
       </c>
-      <c r="Y15" t="n">
-        <v>4.4</v>
-      </c>
       <c r="Z15" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="AA15" t="n">
         <v>21.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>95.3</v>
+        <v>95</v>
       </c>
       <c r="AC15" t="n">
-        <v>-3.8</v>
+        <v>-4.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
         <v>22</v>
       </c>
       <c r="AF15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG15" t="n">
         <v>22</v>
       </c>
       <c r="AH15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI15" t="n">
         <v>23</v>
       </c>
       <c r="AJ15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL15" t="n">
         <v>26</v>
@@ -3135,22 +3202,22 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AO15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR15" t="n">
         <v>25</v>
       </c>
       <c r="AS15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT15" t="n">
         <v>28</v>
@@ -3159,28 +3226,28 @@
         <v>30</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY15" t="n">
         <v>11</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="AZ15" t="n">
         <v>24</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>21</v>
       </c>
       <c r="BA15" t="n">
         <v>9</v>
       </c>
       <c r="BB15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -3209,127 +3276,127 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E16" t="n">
         <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>0.522</v>
+        <v>0.545</v>
       </c>
       <c r="H16" t="n">
         <v>48.2</v>
       </c>
       <c r="I16" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="J16" t="n">
-        <v>82.2</v>
+        <v>82</v>
       </c>
       <c r="K16" t="n">
-        <v>0.445</v>
+        <v>0.449</v>
       </c>
       <c r="L16" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M16" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.338</v>
+        <v>0.339</v>
       </c>
       <c r="O16" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="R16" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="S16" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="T16" t="n">
-        <v>40.2</v>
+        <v>39.9</v>
       </c>
       <c r="U16" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="V16" t="n">
         <v>12.3</v>
       </c>
       <c r="W16" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="X16" t="n">
         <v>6</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>97.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF16" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AG16" t="n">
         <v>15</v>
       </c>
       <c r="AH16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AK16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN16" t="n">
         <v>21</v>
       </c>
-      <c r="AL16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>23</v>
-      </c>
       <c r="AO16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ16" t="n">
         <v>28</v>
       </c>
       <c r="AR16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS16" t="n">
         <v>27</v>
@@ -3338,28 +3405,28 @@
         <v>22</v>
       </c>
       <c r="AU16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV16" t="n">
         <v>1</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX16" t="n">
         <v>6</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ16" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB16" t="n">
         <v>15</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>22</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>17</v>
       </c>
       <c r="BC16" t="n">
         <v>13</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>0.417</v>
+        <v>0.4</v>
       </c>
       <c r="H17" t="n">
         <v>48.6</v>
@@ -3409,46 +3476,46 @@
         <v>36</v>
       </c>
       <c r="J17" t="n">
-        <v>82.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.434</v>
+        <v>0.436</v>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M17" t="n">
         <v>14.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.348</v>
+        <v>0.351</v>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="P17" t="n">
-        <v>26.1</v>
+        <v>25.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R17" t="n">
         <v>13.4</v>
       </c>
       <c r="S17" t="n">
-        <v>30.6</v>
+        <v>30.2</v>
       </c>
       <c r="T17" t="n">
-        <v>44</v>
+        <v>43.6</v>
       </c>
       <c r="U17" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V17" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="W17" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X17" t="n">
         <v>3.7</v>
@@ -3457,31 +3524,31 @@
         <v>5.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-2.2</v>
+        <v>-2.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI17" t="n">
         <v>20</v>
@@ -3490,7 +3557,7 @@
         <v>9</v>
       </c>
       <c r="AK17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL17" t="n">
         <v>24</v>
@@ -3499,34 +3566,34 @@
         <v>26</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP17" t="n">
         <v>9</v>
       </c>
-      <c r="AP17" t="n">
-        <v>8</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR17" t="n">
         <v>2</v>
       </c>
       <c r="AS17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU17" t="n">
         <v>18</v>
       </c>
       <c r="AV17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX17" t="n">
         <v>28</v>
@@ -3538,13 +3605,13 @@
         <v>30</v>
       </c>
       <c r="BA17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BB17" t="n">
         <v>21</v>
       </c>
       <c r="BC17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -3573,37 +3640,37 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.174</v>
+        <v>0.182</v>
       </c>
       <c r="H18" t="n">
         <v>48.7</v>
       </c>
       <c r="I18" t="n">
-        <v>35.8</v>
+        <v>36.1</v>
       </c>
       <c r="J18" t="n">
         <v>84</v>
       </c>
       <c r="K18" t="n">
-        <v>0.427</v>
+        <v>0.43</v>
       </c>
       <c r="L18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M18" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.318</v>
+        <v>0.314</v>
       </c>
       <c r="O18" t="n">
         <v>18.5</v>
@@ -3615,19 +3682,19 @@
         <v>0.766</v>
       </c>
       <c r="R18" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="S18" t="n">
-        <v>29</v>
+        <v>28.6</v>
       </c>
       <c r="T18" t="n">
-        <v>41.6</v>
+        <v>41</v>
       </c>
       <c r="U18" t="n">
         <v>21.7</v>
       </c>
       <c r="V18" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="W18" t="n">
         <v>6.1</v>
@@ -3639,37 +3706,37 @@
         <v>6.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-6.8</v>
+        <v>-6.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>28</v>
       </c>
       <c r="AF18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG18" t="n">
         <v>29</v>
       </c>
       <c r="AH18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AJ18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK18" t="n">
         <v>30</v>
@@ -3681,25 +3748,25 @@
         <v>23</v>
       </c>
       <c r="AN18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR18" t="n">
         <v>6</v>
       </c>
       <c r="AS18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT18" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AU18" t="n">
         <v>8</v>
@@ -3711,7 +3778,7 @@
         <v>29</v>
       </c>
       <c r="AX18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY18" t="n">
         <v>28</v>
@@ -3723,7 +3790,7 @@
         <v>19</v>
       </c>
       <c r="BB18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>-2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
       </c>
       <c r="AF19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG19" t="n">
         <v>16</v>
@@ -3848,13 +3915,13 @@
         <v>9</v>
       </c>
       <c r="AI19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ19" t="n">
         <v>15</v>
       </c>
       <c r="AK19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="n">
         <v>6</v>
@@ -3863,7 +3930,7 @@
         <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO19" t="n">
         <v>5</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F20" t="n">
         <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>0.65</v>
+        <v>0.632</v>
       </c>
       <c r="H20" t="n">
         <v>48</v>
@@ -3958,67 +4025,67 @@
         <v>76.5</v>
       </c>
       <c r="K20" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="M20" t="n">
-        <v>19.2</v>
+        <v>18.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0.407</v>
+        <v>0.41</v>
       </c>
       <c r="O20" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P20" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.819</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="R20" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S20" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="T20" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="U20" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="V20" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W20" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X20" t="n">
         <v>4.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z20" t="n">
         <v>21.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD20" t="n">
         <v>30</v>
       </c>
       <c r="AE20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
         <v>5</v>
@@ -4048,16 +4115,16 @@
         <v>1</v>
       </c>
       <c r="AO20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ20" t="n">
         <v>3</v>
       </c>
       <c r="AR20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS20" t="n">
         <v>23</v>
@@ -4066,16 +4133,16 @@
         <v>27</v>
       </c>
       <c r="AU20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW20" t="n">
         <v>7</v>
       </c>
       <c r="AX20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY20" t="n">
         <v>3</v>
@@ -4084,7 +4151,7 @@
         <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BB20" t="n">
         <v>22</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE21" t="n">
         <v>16</v>
@@ -4245,13 +4312,13 @@
         <v>6</v>
       </c>
       <c r="AT21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU21" t="n">
         <v>5</v>
       </c>
       <c r="AV21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW21" t="n">
         <v>18</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -4301,85 +4368,85 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G22" t="n">
-        <v>0.08</v>
+        <v>0.083</v>
       </c>
       <c r="H22" t="n">
         <v>48</v>
       </c>
       <c r="I22" t="n">
-        <v>35.6</v>
+        <v>35.3</v>
       </c>
       <c r="J22" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="K22" t="n">
-        <v>0.434</v>
+        <v>0.43</v>
       </c>
       <c r="L22" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="M22" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>0.375</v>
+        <v>0.377</v>
       </c>
       <c r="O22" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="P22" t="n">
-        <v>24.4</v>
+        <v>24.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.761</v>
+        <v>0.759</v>
       </c>
       <c r="R22" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S22" t="n">
         <v>29.7</v>
       </c>
       <c r="T22" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U22" t="n">
         <v>19</v>
       </c>
       <c r="V22" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="W22" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X22" t="n">
         <v>4.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z22" t="n">
         <v>22</v>
       </c>
       <c r="AA22" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>93.59999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>-9.9</v>
+        <v>-10.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
         <v>30</v>
@@ -4394,61 +4461,61 @@
         <v>24</v>
       </c>
       <c r="AI22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AJ22" t="n">
         <v>12</v>
       </c>
       <c r="AK22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM22" t="n">
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AR22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AS22" t="n">
         <v>18</v>
       </c>
       <c r="AT22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU22" t="n">
         <v>26</v>
       </c>
       <c r="AV22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX22" t="n">
         <v>19</v>
       </c>
       <c r="AY22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ22" t="n">
         <v>19</v>
       </c>
       <c r="BA22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BB22" t="n">
         <v>29</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>5.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,10 +4640,10 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ23" t="n">
         <v>24</v>
@@ -4594,7 +4661,7 @@
         <v>14</v>
       </c>
       <c r="AO23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP23" t="n">
         <v>5</v>
@@ -4603,19 +4670,19 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS23" t="n">
         <v>8</v>
       </c>
       <c r="AT23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU23" t="n">
         <v>28</v>
       </c>
       <c r="AV23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW23" t="n">
         <v>13</v>
@@ -4630,7 +4697,7 @@
         <v>8</v>
       </c>
       <c r="BA23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>-1.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF24" t="n">
         <v>20</v>
@@ -4755,10 +4822,10 @@
         <v>20</v>
       </c>
       <c r="AH24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ24" t="n">
         <v>10</v>
@@ -4767,7 +4834,7 @@
         <v>24</v>
       </c>
       <c r="AL24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM24" t="n">
         <v>29</v>
@@ -4779,7 +4846,7 @@
         <v>23</v>
       </c>
       <c r="AP24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ24" t="n">
         <v>26</v>
@@ -4794,16 +4861,16 @@
         <v>3</v>
       </c>
       <c r="AU24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AW24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY24" t="n">
         <v>21</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -4925,22 +4992,22 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG25" t="n">
         <v>14</v>
       </c>
       <c r="AH25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ25" t="n">
         <v>29</v>
@@ -4949,7 +5016,7 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM25" t="n">
         <v>14</v>
@@ -4958,10 +5025,10 @@
         <v>6</v>
       </c>
       <c r="AO25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ25" t="n">
         <v>27</v>
@@ -4970,13 +5037,13 @@
         <v>28</v>
       </c>
       <c r="AS25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT25" t="n">
         <v>23</v>
       </c>
       <c r="AU25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV25" t="n">
         <v>30</v>
@@ -4985,13 +5052,13 @@
         <v>24</v>
       </c>
       <c r="AX25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA25" t="n">
         <v>8</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -5029,58 +5096,58 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E26" t="n">
         <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>0.625</v>
+        <v>0.6</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>36.7</v>
+        <v>36.4</v>
       </c>
       <c r="J26" t="n">
-        <v>79.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.462</v>
+        <v>0.457</v>
       </c>
       <c r="L26" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.393</v>
+        <v>0.394</v>
       </c>
       <c r="O26" t="n">
-        <v>17.7</v>
+        <v>17.3</v>
       </c>
       <c r="P26" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.776</v>
+        <v>0.77</v>
       </c>
       <c r="R26" t="n">
         <v>13.3</v>
       </c>
       <c r="S26" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="T26" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U26" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V26" t="n">
         <v>13.1</v>
@@ -5089,64 +5156,64 @@
         <v>6.5</v>
       </c>
       <c r="X26" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.2</v>
+        <v>98.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>6</v>
       </c>
       <c r="AF26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AG26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AH26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AL26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM26" t="n">
         <v>5</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>6</v>
       </c>
       <c r="AN26" t="n">
         <v>3</v>
       </c>
       <c r="AO26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP26" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AQ26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR26" t="n">
         <v>3</v>
@@ -5155,7 +5222,7 @@
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU26" t="n">
         <v>13</v>
@@ -5167,22 +5234,22 @@
         <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY26" t="n">
         <v>1</v>
       </c>
       <c r="AZ26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-8.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
@@ -5301,34 +5368,34 @@
         <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI27" t="n">
         <v>8</v>
       </c>
       <c r="AJ27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL27" t="n">
         <v>25</v>
       </c>
       <c r="AM27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN27" t="n">
         <v>30</v>
       </c>
       <c r="AO27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP27" t="n">
         <v>23</v>
       </c>
       <c r="AQ27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR27" t="n">
         <v>22</v>
@@ -5343,13 +5410,13 @@
         <v>17</v>
       </c>
       <c r="AV27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW27" t="n">
         <v>20</v>
       </c>
       <c r="AX27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY27" t="n">
         <v>15</v>
@@ -5358,10 +5425,10 @@
         <v>28</v>
       </c>
       <c r="BA27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -5393,88 +5460,88 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.652</v>
+        <v>0.636</v>
       </c>
       <c r="H28" t="n">
         <v>48.9</v>
       </c>
       <c r="I28" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J28" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.467</v>
+        <v>0.465</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M28" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0.397</v>
+        <v>0.398</v>
       </c>
       <c r="O28" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="P28" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.754</v>
+        <v>0.756</v>
       </c>
       <c r="R28" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S28" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T28" t="n">
-        <v>40.9</v>
+        <v>41.1</v>
       </c>
       <c r="U28" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V28" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="W28" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="X28" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AF28" t="n">
         <v>7</v>
@@ -5486,31 +5553,31 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="n">
         <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN28" t="n">
         <v>2</v>
       </c>
       <c r="AO28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP28" t="n">
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
@@ -5519,13 +5586,13 @@
         <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU28" t="n">
         <v>7</v>
       </c>
       <c r="AV28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW28" t="n">
         <v>30</v>
@@ -5543,10 +5610,10 @@
         <v>28</v>
       </c>
       <c r="BB28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BC28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -5575,37 +5642,37 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E29" t="n">
         <v>10</v>
       </c>
       <c r="F29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29" t="n">
-        <v>0.435</v>
+        <v>0.455</v>
       </c>
       <c r="H29" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>35.3</v>
+        <v>35.5</v>
       </c>
       <c r="J29" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.451</v>
+        <v>0.453</v>
       </c>
       <c r="L29" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M29" t="n">
-        <v>17</v>
+        <v>16.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0.388</v>
+        <v>0.391</v>
       </c>
       <c r="O29" t="n">
         <v>19.8</v>
@@ -5614,82 +5681,82 @@
         <v>23.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.844</v>
+        <v>0.843</v>
       </c>
       <c r="R29" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="S29" t="n">
-        <v>30</v>
+        <v>30.2</v>
       </c>
       <c r="T29" t="n">
-        <v>38.3</v>
+        <v>38.5</v>
       </c>
       <c r="U29" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V29" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="W29" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="X29" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA29" t="n">
         <v>21.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>97</v>
+        <v>97.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.8</v>
+        <v>-3.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG29" t="n">
         <v>19</v>
       </c>
       <c r="AH29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI29" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL29" t="n">
         <v>14</v>
       </c>
       <c r="AM29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AN29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO29" t="n">
         <v>11</v>
       </c>
       <c r="AP29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5698,7 +5765,7 @@
         <v>30</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT29" t="n">
         <v>29</v>
@@ -5707,13 +5774,13 @@
         <v>4</v>
       </c>
       <c r="AV29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY29" t="n">
         <v>17</v>
@@ -5725,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="BB29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -5841,10 +5908,10 @@
         <v>6</v>
       </c>
       <c r="AF30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH30" t="n">
         <v>24</v>
@@ -5874,7 +5941,7 @@
         <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR30" t="n">
         <v>8</v>
@@ -5883,19 +5950,19 @@
         <v>21</v>
       </c>
       <c r="AT30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW30" t="n">
         <v>3</v>
       </c>
       <c r="AX30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY30" t="n">
         <v>19</v>
@@ -5904,13 +5971,13 @@
         <v>20</v>
       </c>
       <c r="BA30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB30" t="n">
         <v>12</v>
       </c>
       <c r="BC30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6105,7 @@
         <v>14</v>
       </c>
       <c r="AK31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL31" t="n">
         <v>20</v>
@@ -6047,16 +6114,16 @@
         <v>16</v>
       </c>
       <c r="AN31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO31" t="n">
         <v>20</v>
       </c>
       <c r="AP31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ31" t="n">
         <v>17</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>20</v>
       </c>
       <c r="AR31" t="n">
         <v>14</v>
@@ -6071,10 +6138,10 @@
         <v>14</v>
       </c>
       <c r="AV31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX31" t="n">
         <v>22</v>
@@ -6083,13 +6150,13 @@
         <v>13</v>
       </c>
       <c r="AZ31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-14-2008-09</t>
+          <t>2008-12-14</t>
         </is>
       </c>
     </row>
